--- a/consent_forms/037_ai_research_participation_consent_form--consent_forms.xlsx
+++ b/consent_forms/037_ai_research_participation_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_and_acknowledge',_'value':_'acknowledged'}</t>
+          <t>i_understand_and_acknowledge</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'I understand and acknowledge', 'value': 'acknowledged'}</t>
+          <t>I understand and acknowledge</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_consent_to_participate',_'value':_true}</t>
+          <t>yes,_i_consent_to_participate</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I consent to participate', 'value': True}</t>
+          <t>Yes, I consent to participate</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'no,_i_do_not_consent',_'value':_false}</t>
+          <t>no,_i_do_not_consent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'No, I do not consent', 'value': False}</t>
+          <t>No, I do not consent</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_consent_to_anonymized_data_sharing',_'value':_true}</t>
+          <t>yes,_i_consent_to_anonymized_data_sharing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I consent to anonymized data sharing', 'value': True}</t>
+          <t>Yes, I consent to anonymized data sharing</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'no,_only_use_my_data_for_this_specific_study',_'value':_false}</t>
+          <t>no,_only_use_my_data_for_this_specific_study</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'No, only use my data for this specific study', 'value': False}</t>
+          <t>No, only use my data for this specific study</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_consent_to_being_recorded',_'value':_true}</t>
+          <t>yes,_i_consent_to_being_recorded</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I consent to being recorded', 'value': True}</t>
+          <t>Yes, I consent to being recorded</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'no,_i_do_not_consent_to_recording',_'value':_false}</t>
+          <t>no,_i_do_not_consent_to_recording</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'No, I do not consent to recording', 'value': False}</t>
+          <t>No, I do not consent to recording</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable_for_this_study',_'value':_'na'}</t>
+          <t>not_applicable_for_this_study</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not applicable for this study', 'value': 'na'}</t>
+          <t>Not applicable for this study</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_i_can_stop_participating_at_any_time_without_penalty_or_loss_of_compensation.',_'value':_'understood'}</t>
+          <t>i_understand_i_can_stop_participating_at_any_time_without_penalty_or_loss_of_compensation.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'I understand I can stop participating at any time without penalty or loss of compensation.', 'value': 'understood'}</t>
+          <t>I understand I can stop participating at any time without penalty or loss of compensation.</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'i_sign_and_confirm_my_agreement_to_the_terms_above.',_'value':_'signed'}</t>
+          <t>i_sign_and_confirm_my_agreement_to_the_terms_above.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'I sign and confirm my agreement to the terms above.', 'value': 'signed'}</t>
+          <t>I sign and confirm my agreement to the terms above.</t>
         </is>
       </c>
     </row>
